--- a/output/StructureDefinition-RNDSDispensacaoMedicamento.xlsx
+++ b/output/StructureDefinition-RNDSDispensacaoMedicamento.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7383" uniqueCount="895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7383" uniqueCount="896">
   <si>
     <t>Property</t>
   </si>
@@ -1596,6 +1596,10 @@
   </si>
   <si>
     <t>The amount of medication that has been dispensed. Includes unit of measure.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>.quantity</t>
@@ -11805,7 +11809,7 @@
         <v>156</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>347</v>
+        <v>157</v>
       </c>
       <c r="M73" t="s" s="2">
         <v>158</v>
@@ -12037,7 +12041,7 @@
         <v>156</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>392</v>
+        <v>296</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>297</v>
@@ -12154,7 +12158,7 @@
         <v>101</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>394</v>
+        <v>302</v>
       </c>
       <c r="M76" t="s" s="2">
         <v>303</v>
@@ -12271,7 +12275,7 @@
         <v>141</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>396</v>
+        <v>309</v>
       </c>
       <c r="M77" t="s" s="2">
         <v>310</v>
@@ -13326,7 +13330,7 @@
         <v>156</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>398</v>
+        <v>324</v>
       </c>
       <c r="M86" t="s" s="2">
         <v>325</v>
@@ -13562,7 +13566,7 @@
         <v>156</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>347</v>
+        <v>157</v>
       </c>
       <c r="M88" t="s" s="2">
         <v>158</v>
@@ -13794,7 +13798,7 @@
         <v>156</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>392</v>
+        <v>296</v>
       </c>
       <c r="M90" t="s" s="2">
         <v>297</v>
@@ -13911,7 +13915,7 @@
         <v>101</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>394</v>
+        <v>302</v>
       </c>
       <c r="M91" t="s" s="2">
         <v>303</v>
@@ -14028,7 +14032,7 @@
         <v>141</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>396</v>
+        <v>309</v>
       </c>
       <c r="M92" t="s" s="2">
         <v>310</v>
@@ -14145,7 +14149,7 @@
         <v>156</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>398</v>
+        <v>324</v>
       </c>
       <c r="M93" t="s" s="2">
         <v>325</v>
@@ -15732,30 +15736,30 @@
         <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>99</v>
+        <v>506</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15867,10 +15871,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15984,10 +15988,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16010,19 +16014,19 @@
         <v>88</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -16071,7 +16075,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -16089,7 +16093,7 @@
         <v>78</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -16098,15 +16102,15 @@
         <v>78</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16132,20 +16136,20 @@
         <v>107</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q110" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="R110" t="s" s="2">
         <v>78</v>
@@ -16169,10 +16173,10 @@
         <v>176</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>78</v>
@@ -16190,7 +16194,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -16208,7 +16212,7 @@
         <v>78</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -16217,15 +16221,15 @@
         <v>78</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16251,14 +16255,14 @@
         <v>156</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -16307,7 +16311,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -16325,7 +16329,7 @@
         <v>78</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
@@ -16334,15 +16338,15 @@
         <v>78</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16368,14 +16372,14 @@
         <v>101</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>78</v>
@@ -16424,7 +16428,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -16433,7 +16437,7 @@
         <v>87</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>99</v>
@@ -16442,7 +16446,7 @@
         <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -16451,15 +16455,15 @@
         <v>78</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16485,16 +16489,16 @@
         <v>107</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -16543,7 +16547,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -16561,7 +16565,7 @@
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -16570,15 +16574,15 @@
         <v>78</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16604,10 +16608,10 @@
         <v>503</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16658,7 +16662,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -16670,13 +16674,13 @@
         <v>78</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>99</v>
+        <v>506</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>78</v>
@@ -16685,15 +16689,15 @@
         <v>78</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16716,13 +16720,13 @@
         <v>88</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16773,7 +16777,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16791,24 +16795,24 @@
         <v>78</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16831,13 +16835,13 @@
         <v>78</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16888,7 +16892,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16903,27 +16907,27 @@
         <v>99</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16949,10 +16953,10 @@
         <v>375</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -17003,7 +17007,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -17021,24 +17025,24 @@
         <v>78</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17064,10 +17068,10 @@
         <v>285</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -17118,7 +17122,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -17136,13 +17140,13 @@
         <v>78</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>78</v>
@@ -17150,10 +17154,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17265,10 +17269,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17382,10 +17386,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17499,10 +17503,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17616,10 +17620,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17713,7 +17717,7 @@
         <v>78</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>78</v>
@@ -17733,10 +17737,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17848,10 +17852,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17965,10 +17969,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18084,10 +18088,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18203,10 +18207,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18322,10 +18326,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18439,10 +18443,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18554,10 +18558,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18671,10 +18675,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18788,10 +18792,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18814,13 +18818,13 @@
         <v>78</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18871,7 +18875,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18886,10 +18890,10 @@
         <v>99</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>78</v>
@@ -18898,15 +18902,15 @@
         <v>78</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18929,16 +18933,16 @@
         <v>78</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18988,7 +18992,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -19006,7 +19010,7 @@
         <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>78</v>
@@ -19020,10 +19024,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19135,10 +19139,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19252,10 +19256,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19371,10 +19375,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19397,17 +19401,17 @@
         <v>88</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>78</v>
@@ -19456,7 +19460,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -19474,7 +19478,7 @@
         <v>78</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>78</v>
@@ -19483,15 +19487,15 @@
         <v>78</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19517,14 +19521,14 @@
         <v>156</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>78</v>
@@ -19573,7 +19577,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -19591,7 +19595,7 @@
         <v>78</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>78</v>
@@ -19600,15 +19604,15 @@
         <v>78</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19634,16 +19638,16 @@
         <v>183</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>78</v>
@@ -19671,10 +19675,10 @@
         <v>262</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>78</v>
@@ -19692,7 +19696,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19710,7 +19714,7 @@
         <v>78</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>78</v>
@@ -19719,15 +19723,15 @@
         <v>78</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19753,10 +19757,10 @@
         <v>156</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19807,7 +19811,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19825,7 +19829,7 @@
         <v>78</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>78</v>
@@ -19834,15 +19838,15 @@
         <v>78</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19865,19 +19869,19 @@
         <v>88</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
@@ -19926,7 +19930,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19944,7 +19948,7 @@
         <v>78</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>78</v>
@@ -19958,10 +19962,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20073,10 +20077,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20190,10 +20194,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20309,10 +20313,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20335,17 +20339,17 @@
         <v>88</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -20394,7 +20398,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -20412,7 +20416,7 @@
         <v>78</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>78</v>
@@ -20426,10 +20430,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20452,17 +20456,17 @@
         <v>88</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>78</v>
@@ -20511,7 +20515,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20523,13 +20527,13 @@
         <v>78</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>78</v>
@@ -20543,10 +20547,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20658,10 +20662,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20775,10 +20779,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20801,13 +20805,13 @@
         <v>88</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -20858,7 +20862,7 @@
         <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20876,7 +20880,7 @@
         <v>78</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>78</v>
@@ -20890,10 +20894,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20916,19 +20920,19 @@
         <v>88</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>78</v>
@@ -20977,7 +20981,7 @@
         <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -20995,7 +20999,7 @@
         <v>78</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>78</v>
@@ -21009,10 +21013,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21035,13 +21039,13 @@
         <v>88</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21092,7 +21096,7 @@
         <v>78</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -21110,7 +21114,7 @@
         <v>78</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>78</v>
@@ -21124,10 +21128,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21150,19 +21154,19 @@
         <v>88</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>78</v>
@@ -21211,7 +21215,7 @@
         <v>78</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21229,7 +21233,7 @@
         <v>78</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>78</v>
@@ -21243,10 +21247,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21269,19 +21273,19 @@
         <v>88</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
@@ -21330,7 +21334,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21348,7 +21352,7 @@
         <v>78</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>78</v>
@@ -21362,10 +21366,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21391,10 +21395,10 @@
         <v>107</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21424,10 +21428,10 @@
         <v>176</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>78</v>
@@ -21445,7 +21449,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21463,7 +21467,7 @@
         <v>78</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>78</v>
@@ -21477,10 +21481,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21503,13 +21507,13 @@
         <v>88</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21517,7 +21521,7 @@
         <v>78</v>
       </c>
       <c r="Q156" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="R156" t="s" s="2">
         <v>78</v>
@@ -21562,7 +21566,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21580,7 +21584,7 @@
         <v>78</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>78</v>
@@ -21594,10 +21598,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21620,13 +21624,13 @@
         <v>88</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -21677,7 +21681,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21695,7 +21699,7 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>78</v>
@@ -21709,10 +21713,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21735,13 +21739,13 @@
         <v>88</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21792,7 +21796,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21810,7 +21814,7 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>78</v>
@@ -21824,10 +21828,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21850,13 +21854,13 @@
         <v>88</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -21907,7 +21911,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21925,7 +21929,7 @@
         <v>78</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>78</v>
@@ -21939,10 +21943,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21968,10 +21972,10 @@
         <v>107</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -22001,10 +22005,10 @@
         <v>176</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>78</v>
@@ -22022,7 +22026,7 @@
         <v>78</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -22040,7 +22044,7 @@
         <v>78</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>78</v>
@@ -22054,10 +22058,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22083,13 +22087,13 @@
         <v>107</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -22119,7 +22123,7 @@
       </c>
       <c r="Y161" s="2"/>
       <c r="Z161" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>78</v>
@@ -22137,7 +22141,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -22169,10 +22173,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22195,16 +22199,16 @@
         <v>88</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -22254,7 +22258,7 @@
         <v>78</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -22286,10 +22290,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22315,16 +22319,16 @@
         <v>107</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>78</v>
@@ -22352,10 +22356,10 @@
         <v>176</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>78</v>
@@ -22373,7 +22377,7 @@
         <v>78</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -22391,7 +22395,7 @@
         <v>78</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>78</v>
@@ -22405,10 +22409,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22431,13 +22435,13 @@
         <v>88</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -22488,7 +22492,7 @@
         <v>78</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -22506,7 +22510,7 @@
         <v>78</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>78</v>
@@ -22520,10 +22524,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22549,13 +22553,13 @@
         <v>183</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22584,10 +22588,10 @@
         <v>111</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>78</v>
@@ -22605,7 +22609,7 @@
         <v>78</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22623,7 +22627,7 @@
         <v>78</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>78</v>
@@ -22637,10 +22641,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22666,13 +22670,13 @@
         <v>486</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22722,7 +22726,7 @@
         <v>78</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22740,7 +22744,7 @@
         <v>78</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>78</v>
@@ -22749,15 +22753,15 @@
         <v>78</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22783,16 +22787,16 @@
         <v>183</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>78</v>
@@ -22820,10 +22824,10 @@
         <v>262</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>78</v>
@@ -22841,7 +22845,7 @@
         <v>78</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22859,7 +22863,7 @@
         <v>78</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>78</v>
@@ -22868,15 +22872,15 @@
         <v>78</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22902,14 +22906,14 @@
         <v>183</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>78</v>
@@ -22938,7 +22942,7 @@
       </c>
       <c r="Y168" s="2"/>
       <c r="Z168" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>78</v>
@@ -22956,7 +22960,7 @@
         <v>78</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22974,7 +22978,7 @@
         <v>78</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>78</v>
@@ -22983,15 +22987,15 @@
         <v>78</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23103,10 +23107,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23220,10 +23224,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23339,10 +23343,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23454,10 +23458,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23571,10 +23575,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23690,10 +23694,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23807,10 +23811,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23924,10 +23928,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24041,10 +24045,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24160,10 +24164,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24279,10 +24283,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24308,16 +24312,16 @@
         <v>183</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>78</v>
@@ -24345,10 +24349,10 @@
         <v>262</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>78</v>
@@ -24366,7 +24370,7 @@
         <v>78</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
@@ -24384,7 +24388,7 @@
         <v>78</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>78</v>
@@ -24393,15 +24397,15 @@
         <v>78</v>
       </c>
       <c r="AO180" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24424,13 +24428,13 @@
         <v>88</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -24481,7 +24485,7 @@
         <v>78</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
@@ -24508,15 +24512,15 @@
         <v>78</v>
       </c>
       <c r="AO181" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24628,10 +24632,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24745,10 +24749,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24774,14 +24778,14 @@
         <v>183</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>78</v>
@@ -24809,10 +24813,10 @@
         <v>262</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>78</v>
@@ -24830,7 +24834,7 @@
         <v>78</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
@@ -24857,15 +24861,15 @@
         <v>78</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24888,19 +24892,19 @@
         <v>88</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>78</v>
@@ -24929,7 +24933,7 @@
       </c>
       <c r="Y185" s="2"/>
       <c r="Z185" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>78</v>
@@ -24947,7 +24951,7 @@
         <v>78</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
@@ -24965,7 +24969,7 @@
         <v>78</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AM185" t="s" s="2">
         <v>78</v>
@@ -24974,15 +24978,15 @@
         <v>78</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25005,19 +25009,19 @@
         <v>88</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>78</v>
@@ -25066,7 +25070,7 @@
         <v>78</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -25084,7 +25088,7 @@
         <v>78</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AM186" t="s" s="2">
         <v>78</v>
@@ -25093,15 +25097,15 @@
         <v>78</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25124,19 +25128,19 @@
         <v>88</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>78</v>
@@ -25185,7 +25189,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -25203,7 +25207,7 @@
         <v>78</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AM187" t="s" s="2">
         <v>78</v>
@@ -25212,15 +25216,15 @@
         <v>78</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25246,16 +25250,16 @@
         <v>503</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>78</v>
@@ -25304,7 +25308,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -25316,13 +25320,13 @@
         <v>78</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>99</v>
+        <v>506</v>
       </c>
       <c r="AK188" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>78</v>
@@ -25336,10 +25340,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25365,14 +25369,14 @@
         <v>503</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>78</v>
@@ -25421,7 +25425,7 @@
         <v>78</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -25433,13 +25437,13 @@
         <v>78</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>99</v>
+        <v>506</v>
       </c>
       <c r="AK189" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AM189" t="s" s="2">
         <v>78</v>
@@ -25453,10 +25457,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25482,10 +25486,10 @@
         <v>341</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
@@ -25536,7 +25540,7 @@
         <v>78</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
@@ -25554,13 +25558,13 @@
         <v>78</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AM190" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>78</v>
@@ -25568,10 +25572,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25683,10 +25687,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25800,10 +25804,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25919,10 +25923,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25948,10 +25952,10 @@
         <v>486</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -26002,7 +26006,7 @@
         <v>78</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>87</v>
@@ -26020,7 +26024,7 @@
         <v>78</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>78</v>
@@ -26034,10 +26038,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26063,10 +26067,10 @@
         <v>183</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -26096,10 +26100,10 @@
         <v>262</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>78</v>
@@ -26117,7 +26121,7 @@
         <v>78</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
@@ -26141,18 +26145,18 @@
         <v>78</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AO195" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26178,10 +26182,10 @@
         <v>183</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -26211,10 +26215,10 @@
         <v>262</v>
       </c>
       <c r="Y196" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="Z196" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="AA196" t="s" s="2">
         <v>78</v>
@@ -26232,7 +26236,7 @@
         <v>78</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
@@ -26250,13 +26254,13 @@
         <v>78</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>78</v>
@@ -26264,10 +26268,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26293,10 +26297,10 @@
         <v>363</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -26347,7 +26351,7 @@
         <v>78</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>79</v>
@@ -26365,13 +26369,13 @@
         <v>78</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="AM197" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>78</v>
@@ -26379,14 +26383,14 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
@@ -26405,16 +26409,16 @@
         <v>78</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -26464,7 +26468,7 @@
         <v>78</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
@@ -26482,7 +26486,7 @@
         <v>78</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="AM198" t="s" s="2">
         <v>78</v>
@@ -26496,10 +26500,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26522,16 +26526,16 @@
         <v>78</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
@@ -26581,7 +26585,7 @@
         <v>78</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -26599,7 +26603,7 @@
         <v>78</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="AM199" t="s" s="2">
         <v>78</v>
